--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1810-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1810-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7F478DD-9876-4825-84F1-0173B0622053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2118A3C1-7DC2-4DE7-8473-6D1DE8FC5A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DD5C26A5-D6F9-40A2-96BA-B94DFFE0E3EB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2884CF4B-7A6E-4CED-AC06-17B156F476A6}"/>
   </bookViews>
   <sheets>
     <sheet name="1810-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1505,28 +1505,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18684212-2B05-42C6-8804-71180CD09CDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E1A063-7CCC-4E21-B9B2-A970CD6443B8}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="8" width="6.25" customWidth="1"/>
-    <col min="9" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1560,7 +1559,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1596,7 +1595,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1647,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1716,7 +1715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1788,7 +1787,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1860,7 +1859,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1932,7 +1931,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -2004,7 +2003,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2148,7 +2147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2220,7 +2219,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2292,7 +2291,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2364,7 +2363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2436,7 +2435,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2508,7 +2507,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2580,7 +2579,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2652,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2724,7 +2723,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2796,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2868,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2940,7 +2939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -3012,7 +3011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3084,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3156,7 +3155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3300,7 +3299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3372,7 +3371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3444,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3516,7 +3515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3588,7 +3587,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3660,7 +3659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3732,7 +3731,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>1996</v>
       </c>
@@ -3804,7 +3803,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1995</v>
       </c>
@@ -3876,7 +3875,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41"/>
       <c r="B35" s="42"/>
       <c r="C35" s="18" t="s">
@@ -3904,7 +3903,7 @@
       <c r="W35" s="48"/>
       <c r="X35" s="44"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>1994</v>
       </c>
@@ -3976,7 +3975,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1993</v>
       </c>
@@ -4048,7 +4047,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>1992</v>
       </c>
@@ -4120,7 +4119,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1991</v>
       </c>
@@ -4192,7 +4191,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1990</v>
       </c>
@@ -4264,7 +4263,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1989</v>
       </c>
@@ -4336,7 +4335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>1984</v>
       </c>
@@ -4408,7 +4407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
         <v>49</v>
       </c>
